--- a/quizzes/016_pharmacology_mcq_quiz--quizzes.xlsx
+++ b/quizzes/016_pharmacology_mcq_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_a'}</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option A'}</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_b'}</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option B'}</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_c'}</t>
+          <t>option_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option C'}</t>
+          <t>Option C</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'option_d'}</t>
+          <t>option_d</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Option D'}</t>
+          <t>Option D</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_e'}</t>
+          <t>option_e</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option E'}</t>
+          <t>Option E</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_f'}</t>
+          <t>option_f</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option F'}</t>
+          <t>Option F</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_g'}</t>
+          <t>option_g</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option G'}</t>
+          <t>Option G</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'option_h'}</t>
+          <t>option_h</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Option H'}</t>
+          <t>Option H</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'option_i'}</t>
+          <t>option_i</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Option I'}</t>
+          <t>Option I</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'option_j'}</t>
+          <t>option_j</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Option J'}</t>
+          <t>Option J</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'option_k'}</t>
+          <t>option_k</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Option K'}</t>
+          <t>Option K</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'option_l'}</t>
+          <t>option_l</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Option L'}</t>
+          <t>Option L</t>
         </is>
       </c>
     </row>
